--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_112_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_112_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4844</v>
+        <v>5.1072</v>
       </c>
       <c r="E2" t="n">
-        <v>4.052</v>
+        <v>4.4059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4324</v>
+        <v>0.7013</v>
       </c>
       <c r="G2" t="n">
         <v>1.1148</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.847</v>
+        <v>-0.2243</v>
       </c>
       <c r="T2" t="n">
-        <v>0.362</v>
+        <v>0.7158</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2089</v>
+        <v>-0.9401</v>
       </c>
       <c r="V2" t="n">
         <v>3.7527</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9296</v>
+        <v>3.1826</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1221</v>
+        <v>0.476</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8075</v>
+        <v>2.7066</v>
       </c>
       <c r="G3" t="n">
         <v>6.0751</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2719</v>
+        <v>-0.0189</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1766</v>
+        <v>0.1772</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0953</v>
+        <v>-0.1961</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3935</v>
+        <v>2.3428</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5324</v>
+        <v>2.4145</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1389</v>
+        <v>-0.0716</v>
       </c>
       <c r="G4" t="n">
         <v>1.8051</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6581</v>
+        <v>0.6073</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6607</v>
+        <v>0.5427</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0026</v>
+        <v>0.0646</v>
       </c>
       <c r="V4" t="n">
         <v>0.3943</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2901</v>
+        <v>1.5095</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9166</v>
+        <v>-1.5627</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2066</v>
+        <v>3.0722</v>
       </c>
       <c r="G5" t="n">
         <v>3.86</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.145</v>
+        <v>0.0745</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1019</v>
+        <v>0.2519</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.043</v>
+        <v>-0.1775</v>
       </c>
       <c r="V5" t="n">
         <v>1.7501</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0211</v>
+        <v>-0.004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0867</v>
+        <v>0.0313</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0353</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4846</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2324</v>
+        <v>-0.2153</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0905</v>
+        <v>0.2084</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3229</v>
+        <v>-0.4237</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.439</v>
+        <v>-0.3046</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7814</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3423</v>
+        <v>0.4768</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4385</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3743</v>
+        <v>-0.2399</v>
       </c>
       <c r="T7" t="n">
         <v>-0.224</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1502</v>
+        <v>-0.0158</v>
       </c>
       <c r="V7" t="n">
         <v>0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5245</v>
+        <v>-0.4909</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5245</v>
+        <v>-0.4909</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5469000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6523</v>
+        <v>-1.8382</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7802</v>
+        <v>-2.134</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1278</v>
+        <v>0.2959</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2486</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1709</v>
+        <v>-0.0149</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7591</v>
+        <v>0.4052</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.4202</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6468</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.279</v>
+        <v>-3.1883</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.764</v>
+        <v>-1.4717</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.515</v>
+        <v>-1.7166</v>
       </c>
       <c r="G10" t="n">
         <v>0.4253</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5456</v>
+        <v>-0.3637</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2151</v>
+        <v>0.5074</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6695</v>
+        <v>-0.8711</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9304</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8478</v>
+        <v>-3.9822</v>
       </c>
       <c r="E11" t="n">
         <v>-2.6083</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2394</v>
+        <v>-1.3739</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8225</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0975</v>
+        <v>-0.232</v>
       </c>
       <c r="T11" t="n">
         <v>0.0905</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.188</v>
+        <v>-0.3224</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.333899999999999</v>
+        <v>2.3339</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2307</v>
+        <v>-1.2304</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5644</v>
+        <v>3.564500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>8.7392</v>
@@ -1390,13 +1390,13 @@
         <v>9.2784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5711000000000002</v>
+        <v>-0.5712</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6754</v>
+        <v>2.6751</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.2462</v>
+        <v>-3.246300000000001</v>
       </c>
       <c r="V12" t="n">
         <v>4.6035</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2253</v>
+        <v>2.9904</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6399</v>
+        <v>2.2265</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5854</v>
+        <v>0.7639</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1831</v>
+        <v>-0.175</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5172</v>
+        <v>0.2533</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6659</v>
+        <v>-0.4283</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9224</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8856</v>
+        <v>0.9579</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0368</v>
+        <v>-0.3213</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2606</v>
+        <v>-0.8116</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3684</v>
+        <v>-0.7045</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6291</v>
+        <v>-0.107</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6685</v>
+        <v>1.382</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1993</v>
+        <v>1.0539</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4692</v>
+        <v>0.3282</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
         <v>-1.0722</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0019</v>
+        <v>2.5535</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4624</v>
+        <v>-0.4474</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5394</v>
+        <v>3.0009</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.175</v>
+        <v>0.5258</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2533</v>
+        <v>1.9747</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4283</v>
+        <v>-1.449</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.4261</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9579</v>
+        <v>2.5544</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3213</v>
+        <v>-2.1283</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8116</v>
+        <v>0.0997</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7045</v>
+        <v>-0.5796</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.107</v>
+        <v>0.6793</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3935</v>
+        <v>0.2596</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2898</v>
+        <v>0.3738</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1037</v>
+        <v>-0.1142</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.013</v>
+        <v>2.288</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1491</v>
+        <v>1.8142</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1361</v>
+        <v>0.4738</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7731</v>
+        <v>2.1831</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.5172</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.174</v>
+        <v>0.6659</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8266</v>
+        <v>1.9224</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7897999999999999</v>
+        <v>1.8856</v>
       </c>
       <c r="L15" t="n">
         <v>0.0368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0535</v>
+        <v>0.2606</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1573</v>
+        <v>-0.3684</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2108</v>
+        <v>0.6291</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4718</v>
+        <v>0.7312</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7863</v>
+        <v>0.3736</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3145</v>
+        <v>0.3576</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5361</v>
+        <v>-0.3943</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3205</v>
+        <v>1.9737</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1665</v>
+        <v>1.7952</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8461</v>
+        <v>0.1784</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9536</v>
+        <v>0.7731</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8466</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.107</v>
+        <v>-0.174</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.8266</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5517</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0502</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4551</v>
+        <v>-0.0535</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3983</v>
+        <v>0.1573</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0568</v>
+        <v>-0.2108</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7948</v>
+        <v>0.4325</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7526</v>
+        <v>0.4325</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4988</v>
+        <v>0.235</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6269</v>
+        <v>0.157</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1258</v>
+        <v>0.078</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5258</v>
+        <v>1.0545</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9747</v>
+        <v>1.9579</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.449</v>
+        <v>-0.9034</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4261</v>
+        <v>1.1121</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5544</v>
+        <v>2.5375</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1283</v>
+        <v>-1.4255</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0997</v>
+        <v>-0.0576</v>
       </c>
       <c r="N17" t="n">
         <v>-0.5796</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6793</v>
+        <v>0.5221</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0154</v>
+        <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.795</v>
+        <v>0.1652</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8057</v>
+        <v>0.2047</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9893</v>
+        <v>-0.0395</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.235</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6288</v>
+        <v>-1.4127</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3938</v>
+        <v>0.8879</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0545</v>
+        <v>-2.2558</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9579</v>
+        <v>-1.6434</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9034</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1121</v>
+        <v>-0.9687</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5375</v>
+        <v>-0.4131</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4255</v>
+        <v>-0.5556</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0576</v>
+        <v>-1.287</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5796</v>
+        <v>-1.2303</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5221</v>
+        <v>-0.0568</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1652</v>
+        <v>-1.0034</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6765</v>
+        <v>-0.4439</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5113</v>
+        <v>-0.5594</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1444</v>
+        <v>0.6468</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7973</v>
+        <v>-0.6458</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7738</v>
+        <v>-0.6559</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0235</v>
+        <v>0.0101</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0672</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0523</v>
+        <v>0.0993</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1418</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6085</v>
+        <v>-0.7684</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2383</v>
+        <v>1.2793</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6298</v>
+        <v>-2.0477</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2558</v>
+        <v>-0.9536</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6434</v>
+        <v>-0.8466</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.107</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9687</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4131</v>
+        <v>0.5517</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5556</v>
+        <v>-0.0502</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.287</v>
+        <v>-1.4551</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2303</v>
+        <v>-1.3983</v>
       </c>
       <c r="O20" t="n">
         <v>-0.0568</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0871</v>
+        <v>0.7059</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2696</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8175</v>
+        <v>-0.1595</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6468</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6468</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7858</v>
+        <v>-0.982</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1453</v>
+        <v>-2.1537</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3595</v>
+        <v>1.1716</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6533</v>
+        <v>-2.7498</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6063</v>
+        <v>-1.0432</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.047</v>
+        <v>-1.7066</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.577</v>
+        <v>-2.6531</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.376</v>
+        <v>-0.6855</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.201</v>
+        <v>-1.9676</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0762</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2303</v>
+        <v>-0.3577</v>
       </c>
       <c r="O21" t="n">
-        <v>0.154</v>
+        <v>0.261</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1505</v>
+        <v>0.6596</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4086</v>
+        <v>0.4995</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.742</v>
+        <v>0.1601</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9707</v>
+        <v>-1.3654</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8614</v>
+        <v>-2.0274</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8907</v>
+        <v>0.662</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7498</v>
+        <v>-1.6533</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0432</v>
+        <v>-1.6063</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7066</v>
+        <v>-0.047</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6531</v>
+        <v>-0.577</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6855</v>
+        <v>-0.376</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9676</v>
+        <v>-0.201</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-1.0762</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3577</v>
+        <v>-1.2303</v>
       </c>
       <c r="O22" t="n">
-        <v>0.261</v>
+        <v>0.154</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.329</v>
+        <v>-0.7301</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2082</v>
+        <v>-0.2906</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1208</v>
+        <v>-0.4395</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4408</v>
+        <v>-1.7717</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5843</v>
+        <v>-1.9945</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1435</v>
+        <v>0.2228</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1005</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8764</v>
+        <v>-0.2074</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8962</v>
+        <v>-0.3064</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0198</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0253</v>
+        <v>-3.9574</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3812</v>
+        <v>-2.1453</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.644</v>
+        <v>-1.812</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3207</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3677</v>
+        <v>0.4356</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2047</v>
+        <v>0.4406</v>
       </c>
       <c r="U24" t="n">
-        <v>0.163</v>
+        <v>-0.005</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.333899999999999</v>
+        <v>0.025199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.564500000000001</v>
+        <v>-3.5647</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2306</v>
+        <v>3.5897</v>
       </c>
       <c r="G25" t="n">
         <v>-8.7394</v>
@@ -2386,7 +2386,7 @@
         <v>-6.7768</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.239699999999999</v>
+        <v>-6.2397</v>
       </c>
       <c r="N25" t="n">
         <v>-8.0474</v>
@@ -2404,13 +2404,13 @@
         <v>19.716</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5712000000000002</v>
+        <v>2.93</v>
       </c>
       <c r="T25" t="n">
-        <v>3.246200000000001</v>
+        <v>3.2464</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.6751</v>
+        <v>-0.3161</v>
       </c>
       <c r="V25" t="n">
         <v>-4.6035</v>
